--- a/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/DuomenysTestui/zive_irasai_testui_isplestas_updated_1024_0_5_3_7_0_12.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AtsisiuntimasZiveDuomenu/DuomenysTestui/zive_irasai_testui_isplestas_updated_1024_0_5_3_7_0_12.xlsx
@@ -556,7 +556,11 @@
     <col width="4.90625" customWidth="1" min="12" max="12"/>
     <col hidden="1" width="4.7265625" customWidth="1" min="13" max="13"/>
     <col hidden="1" width="5.26953125" customWidth="1" min="14" max="14"/>
-    <col hidden="1" width="4.90625" customWidth="1" min="15" max="19"/>
+    <col hidden="1" width="4.90625" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
     <col width="8.90625" customWidth="1" min="20" max="20"/>
     <col width="9.26953125" customWidth="1" min="21" max="21"/>
     <col width="9.7265625" customWidth="1" style="9" min="22" max="26"/>
@@ -2205,7 +2209,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2216,7 +2220,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>/home/kesju/DI/2025_ZIVEO/PROJECT_TRAIN_UNET/MODEL_UNET</t>
+          <t>/home/kestutis/DI/2025_ZIVEO/PROJECT_TRAIN_UNET/MODEL_UNET</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2255,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>/home/kesju/DI/2025_ZIVEO/PROJECT_TRAIN_UNET/MODEL_VU_CNN</t>
+          <t>/home/kestutis/DI/2025_ZIVEO/PROJECT_TRAIN_UNET/MODEL_VU_CNN</t>
         </is>
       </c>
     </row>
